--- a/seminars/iso-14971-risk-management/ISO-14971-Risk-File-Toolkit.xlsx
+++ b/seminars/iso-14971-risk-management/ISO-14971-Risk-File-Toolkit.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="747">
   <si>
     <t xml:space="preserve">ISO 14971 Risk File Toolkit</t>
   </si>
@@ -171,7 +171,13 @@
     <t xml:space="preserve">A note on FDA</t>
   </si>
   <si>
-    <t xml:space="preserve">ISO 14971 is not incorporated by reference into 21 CFR Part 820. The risk management obligation FDA enforces runs through the ISO 13485:2016 clauses that Part 820 does incorporate, principally 4.1.2 b), 7.1, and the design, purchasing, production and measurement clauses. ISO 14971:2019 is an FDA-recognized consensus standard, so conformance can be declared in a submission; recognition is not incorporation.</t>
+    <t xml:space="preserve">ISO 14971 is not incorporated by reference into 21 CFR Part 820, which incorporates ISO 13485:2016 and Clause 3 of ISO 9000:2015 and nothing else (QMSR final rule, Comment 9, 89 FR 7503). The risk management obligation FDA enforces runs through the ISO 13485:2016 clauses that Part 820 does incorporate, principally 4.1.2 b), 7.1, and the design, purchasing, production and measurement clauses; FDA named 4.1, 7.1, 7.3, 7.4, 7.5, 7.6 and 8.2 in its response to Comment 19. ISO 14971:2019 is an FDA-recognized consensus standard at recognition number 5-125, complete standard, so conformance can be declared in a submission; recognition is not incorporation. The string 14971 appears nowhere in the 78 pages of Compliance Program 7382.850.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No quantitative requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDA stated at its 14 January 2026 town hall that there is no QMSR or ISO 13485 requirement for a quantitative description of risk. A semi-quantitative scoring scheme like the one on the Scales sheet is a choice you make and must justify, not an obligation you inherit.</t>
   </si>
   <si>
     <t xml:space="preserve">Verify before you rely on it</t>
@@ -322,6 +328,18 @@
   </si>
   <si>
     <t xml:space="preserve">ISO 14971 Clause 4.3 requires the persons performing risk management tasks to be competent, with records. ISO 13485 Clause 6.2 is the QMS hook FDA inspects. Name the competence requirement and where the records live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A clinical expert assigned to the risk management team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team-NB's best practice guidance on technical documentation (V4, 21 April 2026) closes its list of risk management plan contents with a requirement for qualified persons, including the assignment of a clinical expert. Most plans name engineering and quality roles and stop. P2 is a clinical judgement, so somebody clinical has to own it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity, use-environment and user-competence hazards in scope of the analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team-NB section 5.3 names hazards related to cybersecurity, to ergonomic features, to the use environment, and to the technical knowledge, experience, education and training of the intended users. Say in the plan that these classes are in scope, because a reviewer will check whether the analysis reached them.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan revision control</t>
@@ -3129,7 +3147,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3350,7 +3368,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
@@ -3358,24 +3376,32 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-    </row>
-    <row r="36" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+    <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3404,485 +3430,485 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">COUNTA('Hazard Analysis'!$A$5:$A$44)</f>
         <v>16</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B7" s="38" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$A$5:$A$44,"&lt;&gt;",'Hazard Analysis'!$G$5:$G$44,"")</f>
         <v>1</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B8" s="36" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$A$5:$A$44,"&lt;&gt;",'Hazard Analysis'!$K$5:$K$44,"")</f>
         <v>1</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B9" s="38" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$M$5:$M$44,"*S only*")</f>
         <v>0</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$M$5:$M$44,"Not acceptable*")</f>
         <v>9</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B14" s="38" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$M$5:$M$44,"Not acceptable*",'Hazard Analysis'!$P$5:$P$44,"")</f>
         <v>0</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B15" s="36" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$Q$5:$Q$44,3)</f>
         <v>3</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B16" s="38" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$D$5:$D$34,"&gt;1",'Risk Controls'!$E$5:$E$34,"")</f>
         <v>1</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B17" s="36" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$A$5:$A$34,"&lt;&gt;",'Risk Controls'!$G$5:$G$34,"")</f>
         <v>0</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B18" s="38" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$A$5:$A$34,"&lt;&gt;",'Risk Controls'!$H$5:$H$34,"")</f>
         <v>1</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B19" s="36" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$A$5:$A$34,"&lt;&gt;",'Risk Controls'!$J$5:$J$34,"")</f>
         <v>1</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B20" s="38" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$A$5:$A$34,"&lt;&gt;",'Risk Controls'!$K$5:$K$34,0)</f>
         <v>0</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B24" s="36" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$V$5:$V$44,"Not acceptable*")</f>
         <v>4</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B25" s="38" t="n">
         <f aca="false">SUMPRODUCT(('Hazard Analysis'!$V$5:$V$44&lt;&gt;"")*(LEFT('Hazard Analysis'!$V$5:$V$44,3)="Not")*(COUNTIF('Benefit-Risk'!$A$5:$A$16,'Hazard Analysis'!$A$5:$A$44)=0))</f>
         <v>0</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B26" s="36" t="n">
         <f aca="false">COUNTIFS('Benefit-Risk'!$A$5:$A$16,"&lt;&gt;",'Benefit-Risk'!$L$5:$L$16,"&lt;&gt;Complete")</f>
         <v>1</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B27" s="38" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$Q$5:$Q$44,3,'Hazard Analysis'!$Z$5:$Z$44,"")</f>
         <v>1</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B28" s="36" t="str">
         <f aca="false">'Residual Risk'!$C$29 &amp; " of 9"</f>
         <v>0 of 9</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="B32" s="36" t="n">
         <f aca="false">COUNTA('Prod &amp; Post-Prod'!$A$5:$A$34)</f>
         <v>5</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B33" s="38" t="n">
         <f aca="false">COUNTIFS('Prod &amp; Post-Prod'!$A$5:$A$34,"&lt;&gt;",'Prod &amp; Post-Prod'!$S$5:$S$34,"&lt;&gt;Closed")</f>
         <v>2</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="B34" s="36" t="n">
         <f aca="false">COUNTIF('Prod &amp; Post-Prod'!$R$5:$R$34,"OVERDUE")</f>
         <v>0</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B35" s="38" t="n">
         <f aca="false">COUNTIFS('Prod &amp; Post-Prod'!$A$5:$A$34,"&lt;&gt;",'Prod &amp; Post-Prod'!$R$5:$R$34,"&lt;&gt;OK")</f>
         <v>1</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="B36" s="36" t="n">
         <f aca="false">COUNTIF('Prod &amp; Post-Prod'!$R$5:$R$34,"Risk file rows not updated")</f>
         <v>1</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="B40" s="36" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$A$5:$A$44,"&lt;&gt;",'Hazard Analysis'!$X$5:$X$44,"&lt;&gt;Complete")</f>
         <v>2</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="B41" s="38" t="n">
         <f aca="false">COUNTIFS('Risk Controls'!$A$5:$A$34,"&lt;&gt;",'Risk Controls'!$L$5:$L$34,"&lt;&gt;Complete")</f>
         <v>1</v>
       </c>
       <c r="C41" s="52" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B42" s="36" t="str">
         <f aca="false">'RM File Index'!$D$36</f>
         <v>Not started</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B47" s="53" t="str">
         <f aca="false">IF($B$14=0,"Yes","No - " &amp; $B$14 &amp; " outstanding")</f>
         <v>Yes</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B48" s="54" t="str">
         <f aca="false">IF($B$17+$B$18=0,"Yes","No - " &amp; ($B$17+$B$18) &amp; " missing")</f>
         <v>No - 1 missing</v>
       </c>
       <c r="C48" s="52" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B49" s="53" t="str">
         <f aca="false">IF($B$25+$B$26=0,"Yes","No - " &amp; ($B$25+$B$26) &amp; " outstanding")</f>
         <v>No - 1 outstanding</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="B50" s="54" t="str">
         <f aca="false">IF('Residual Risk'!$C$30="","No",IF('Residual Risk'!$C$29&lt;9,"No - " &amp; (9-'Residual Risk'!$C$29) &amp; " inputs not considered","Yes"))</f>
         <v>No</v>
       </c>
       <c r="C50" s="52" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B51" s="53" t="str">
         <f aca="false">IF($B$40+$B$41=0,"Yes","No - " &amp; ($B$40+$B$41) &amp; " rows incomplete")</f>
         <v>No - 3 rows incomplete</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B52" s="54" t="str">
         <f aca="false">IF($B$33+$B$34=0,"Yes","No - " &amp; ($B$33+$B$34) &amp; " open or overdue")</f>
         <v>No - 2 open or overdue</v>
       </c>
       <c r="C52" s="52" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -3901,7 +3927,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3914,43 +3940,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -3958,13 +3984,13 @@
     </row>
     <row r="6" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -3972,13 +3998,13 @@
     </row>
     <row r="7" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -3986,13 +4012,13 @@
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -4000,13 +4026,13 @@
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -4014,13 +4040,13 @@
     </row>
     <row r="10" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -4028,13 +4054,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -4042,13 +4068,13 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -4056,13 +4082,13 @@
     </row>
     <row r="13" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -4070,13 +4096,13 @@
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -4084,13 +4110,13 @@
     </row>
     <row r="15" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -4098,13 +4124,13 @@
     </row>
     <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -4112,13 +4138,13 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -4126,35 +4152,63 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
+    <row r="20" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E19" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E21" type="list">
       <formula1>"Yes,Partial,No,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4183,32 +4237,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F5" s="5"/>
     </row>
@@ -4217,14 +4271,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -4233,14 +4287,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F7" s="8"/>
     </row>
@@ -4249,14 +4303,14 @@
         <v>3</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -4265,14 +4319,14 @@
         <v>2</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F9" s="8"/>
     </row>
@@ -4281,25 +4335,25 @@
         <v>1</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -4309,17 +4363,17 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F13" s="5"/>
     </row>
@@ -4328,10 +4382,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="17" t="n">
@@ -4344,10 +4398,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="18" t="n">
@@ -4360,10 +4414,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="17" t="n">
@@ -4376,10 +4430,10 @@
         <v>2</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="18" t="n">
@@ -4392,10 +4446,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="17" t="n">
@@ -4405,12 +4459,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -4420,17 +4474,17 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F22" s="5"/>
     </row>
@@ -4439,10 +4493,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="17" t="n">
@@ -4455,10 +4509,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="18" t="n">
@@ -4471,10 +4525,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="17" t="n">
@@ -4487,10 +4541,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="18" t="n">
@@ -4503,10 +4557,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="17" t="n">
@@ -4516,12 +4570,12 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -4531,27 +4585,27 @@
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>5</v>
@@ -4571,7 +4625,7 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B33" s="20" t="n">
         <v>4</v>
@@ -4591,7 +4645,7 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>3</v>
@@ -4611,7 +4665,7 @@
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B35" s="22" t="n">
         <v>2</v>
@@ -4631,7 +4685,7 @@
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B36" s="22" t="n">
         <v>1</v>
@@ -4651,12 +4705,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -4666,7 +4720,7 @@
     </row>
     <row r="40" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -4676,132 +4730,132 @@
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="16" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -4899,118 +4953,118 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>4</v>
@@ -5022,7 +5076,7 @@
         <v>4</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L5" s="28" t="n">
         <f aca="false">IF($H5="","",IF($H5=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H5,6-$I5)))</f>
@@ -5041,7 +5095,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P5" s="26" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q5" s="27" t="n">
         <v>1</v>
@@ -5072,34 +5126,34 @@
         <v>Complete</v>
       </c>
       <c r="Y5" s="26" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Z5" s="26"/>
       <c r="AA5" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>4</v>
@@ -5111,7 +5165,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="L6" s="31" t="n">
         <f aca="false">IF($H6="","",IF($H6=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H6,6-$I6)))</f>
@@ -5130,7 +5184,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q6" s="27" t="n">
         <v>1</v>
@@ -5161,34 +5215,34 @@
         <v>Complete</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z6" s="26"/>
       <c r="AA6" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>3</v>
@@ -5200,7 +5254,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L7" s="28" t="n">
         <f aca="false">IF($H7="","",IF($H7=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H7,6-$I7)))</f>
@@ -5219,7 +5273,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P7" s="26" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q7" s="27" t="n">
         <v>2</v>
@@ -5250,34 +5304,34 @@
         <v>Complete</v>
       </c>
       <c r="Y7" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z7" s="26"/>
       <c r="AA7" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>4</v>
@@ -5289,7 +5343,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L8" s="31" t="n">
         <f aca="false">IF($H8="","",IF($H8=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H8,6-$I8)))</f>
@@ -5308,7 +5362,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P8" s="26" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q8" s="27" t="n">
         <v>2</v>
@@ -5339,34 +5393,34 @@
         <v>Complete</v>
       </c>
       <c r="Y8" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Z8" s="26"/>
       <c r="AA8" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>3</v>
@@ -5378,7 +5432,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L9" s="28" t="n">
         <f aca="false">IF($H9="","",IF($H9=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H9,6-$I9)))</f>
@@ -5397,7 +5451,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P9" s="26" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q9" s="27" t="n">
         <v>2</v>
@@ -5428,34 +5482,34 @@
         <v>Complete</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z9" s="26"/>
       <c r="AA9" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>2</v>
@@ -5467,7 +5521,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="L10" s="31" t="n">
         <f aca="false">IF($H10="","",IF($H10=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H10,6-$I10)))</f>
@@ -5486,7 +5540,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P10" s="26" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q10" s="27" t="n">
         <v>1</v>
@@ -5517,34 +5571,34 @@
         <v>Complete</v>
       </c>
       <c r="Y10" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z10" s="26"/>
       <c r="AA10" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>2</v>
@@ -5556,7 +5610,7 @@
         <v>5</v>
       </c>
       <c r="K11" s="26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="L11" s="28" t="n">
         <f aca="false">IF($H11="","",IF($H11=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H11,6-$I11)))</f>
@@ -5575,7 +5629,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P11" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q11" s="27" t="n">
         <v>1</v>
@@ -5606,34 +5660,34 @@
         <v>Complete</v>
       </c>
       <c r="Y11" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z11" s="26"/>
       <c r="AA11" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>2</v>
@@ -5645,7 +5699,7 @@
         <v>4</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="L12" s="31" t="n">
         <f aca="false">IF($H12="","",IF($H12=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H12,6-$I12)))</f>
@@ -5664,7 +5718,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P12" s="26" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q12" s="27" t="n">
         <v>1</v>
@@ -5695,34 +5749,34 @@
         <v>Complete</v>
       </c>
       <c r="Y12" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z12" s="26"/>
       <c r="AA12" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H13" s="27" t="n">
         <v>5</v>
@@ -5734,7 +5788,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="26" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L13" s="28" t="n">
         <f aca="false">IF($H13="","",IF($H13=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H13,6-$I13)))</f>
@@ -5753,7 +5807,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P13" s="26" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="Q13" s="27" t="n">
         <v>1</v>
@@ -5784,34 +5838,34 @@
         <v>Complete</v>
       </c>
       <c r="Y13" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z13" s="26"/>
       <c r="AA13" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>3</v>
@@ -5823,7 +5877,7 @@
         <v>3</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="L14" s="31" t="n">
         <f aca="false">IF($H14="","",IF($H14=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H14,6-$I14)))</f>
@@ -5842,7 +5896,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P14" s="26" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q14" s="27" t="n">
         <v>2</v>
@@ -5873,34 +5927,34 @@
         <v>Complete</v>
       </c>
       <c r="Y14" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z14" s="26"/>
       <c r="AA14" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H15" s="27" t="n">
         <v>3</v>
@@ -5912,7 +5966,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="26" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="L15" s="28" t="n">
         <f aca="false">IF($H15="","",IF($H15=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H15,6-$I15)))</f>
@@ -5931,7 +5985,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P15" s="26" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="Q15" s="27" t="n">
         <v>3</v>
@@ -5962,36 +6016,36 @@
         <v>Complete</v>
       </c>
       <c r="Y15" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z15" s="26" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>2</v>
@@ -6003,7 +6057,7 @@
         <v>5</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="L16" s="31" t="n">
         <f aca="false">IF($H16="","",IF($H16=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H16,6-$I16)))</f>
@@ -6022,7 +6076,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P16" s="26" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q16" s="27" t="n">
         <v>1</v>
@@ -6053,34 +6107,34 @@
         <v>Complete</v>
       </c>
       <c r="Y16" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z16" s="26"/>
       <c r="AA16" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H17" s="27" t="n">
         <v>3</v>
@@ -6092,7 +6146,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="L17" s="28" t="n">
         <f aca="false">IF($H17="","",IF($H17=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H17,6-$I17)))</f>
@@ -6111,7 +6165,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P17" s="26" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="Q17" s="27" t="n">
         <v>3</v>
@@ -6142,36 +6196,36 @@
         <v>Complete</v>
       </c>
       <c r="Y17" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z17" s="26" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>3</v>
@@ -6183,7 +6237,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="L18" s="31" t="n">
         <f aca="false">IF($H18="","",IF($H18=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H18,6-$I18)))</f>
@@ -6202,7 +6256,7 @@
         <v>Consider AFAP</v>
       </c>
       <c r="P18" s="26" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="Q18" s="27" t="n">
         <v>2</v>
@@ -6233,33 +6287,33 @@
         <v>Complete</v>
       </c>
       <c r="Y18" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z18" s="26" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="27" t="n">
@@ -6312,30 +6366,30 @@
       <c r="Y19" s="26"/>
       <c r="Z19" s="26"/>
       <c r="AA19" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>5</v>
@@ -6347,7 +6401,7 @@
         <v>4</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="L20" s="31" t="n">
         <f aca="false">IF($H20="","",IF($H20=0,"n/e",INDEX(Scales!$B$32:$F$36,6-$H20,6-$I20)))</f>
@@ -6366,7 +6420,7 @@
         <v>Yes - Clause 7.1</v>
       </c>
       <c r="P20" s="26" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="Q20" s="27" t="n">
         <v>3</v>
@@ -6397,11 +6451,11 @@
         <v>Effectiveness not verified</v>
       </c>
       <c r="Y20" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Z20" s="26"/>
       <c r="AA20" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7732,88 +7786,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="K5" s="34" t="n">
         <f aca="false">IF($A5="","",COUNTIF('Hazard Analysis'!$P:$P,$A5))</f>
@@ -7825,39 +7879,39 @@
       </c>
       <c r="M5" s="26"/>
       <c r="N5" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="K6" s="35" t="n">
         <f aca="false">IF($A6="","",COUNTIF('Hazard Analysis'!$P:$P,$A6))</f>
@@ -7869,39 +7923,39 @@
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="K7" s="34" t="n">
         <f aca="false">IF($A7="","",COUNTIF('Hazard Analysis'!$P:$P,$A7))</f>
@@ -7913,39 +7967,39 @@
       </c>
       <c r="M7" s="26"/>
       <c r="N7" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D8" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="K8" s="35" t="n">
         <f aca="false">IF($A8="","",COUNTIF('Hazard Analysis'!$P:$P,$A8))</f>
@@ -7957,39 +8011,39 @@
       </c>
       <c r="M8" s="26"/>
       <c r="N8" s="26" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="K9" s="34" t="n">
         <f aca="false">IF($A9="","",COUNTIF('Hazard Analysis'!$P:$P,$A9))</f>
@@ -8001,39 +8055,39 @@
       </c>
       <c r="M9" s="26"/>
       <c r="N9" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D10" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="K10" s="35" t="n">
         <f aca="false">IF($A10="","",COUNTIF('Hazard Analysis'!$P:$P,$A10))</f>
@@ -8045,39 +8099,39 @@
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="K11" s="34" t="n">
         <f aca="false">IF($A11="","",COUNTIF('Hazard Analysis'!$P:$P,$A11))</f>
@@ -8089,39 +8143,39 @@
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="26" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D12" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="K12" s="35" t="n">
         <f aca="false">IF($A12="","",COUNTIF('Hazard Analysis'!$P:$P,$A12))</f>
@@ -8133,39 +8187,39 @@
       </c>
       <c r="M12" s="26"/>
       <c r="N12" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K13" s="34" t="n">
         <f aca="false">IF($A13="","",COUNTIF('Hazard Analysis'!$P:$P,$A13))</f>
@@ -8177,39 +8231,39 @@
       </c>
       <c r="M13" s="26"/>
       <c r="N13" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D14" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="K14" s="35" t="n">
         <f aca="false">IF($A14="","",COUNTIF('Hazard Analysis'!$P:$P,$A14))</f>
@@ -8221,39 +8275,39 @@
       </c>
       <c r="M14" s="26"/>
       <c r="N14" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="K15" s="34" t="n">
         <f aca="false">IF($A15="","",COUNTIF('Hazard Analysis'!$P:$P,$A15))</f>
@@ -8265,39 +8319,39 @@
       </c>
       <c r="M15" s="26"/>
       <c r="N15" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D16" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="K16" s="35" t="n">
         <f aca="false">IF($A16="","",COUNTIF('Hazard Analysis'!$P:$P,$A16))</f>
@@ -8309,39 +8363,39 @@
       </c>
       <c r="M16" s="26"/>
       <c r="N16" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="K17" s="34" t="n">
         <f aca="false">IF($A17="","",COUNTIF('Hazard Analysis'!$P:$P,$A17))</f>
@@ -8353,39 +8407,39 @@
       </c>
       <c r="M17" s="26"/>
       <c r="N17" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="K18" s="35" t="n">
         <f aca="false">IF($A18="","",COUNTIF('Hazard Analysis'!$P:$P,$A18))</f>
@@ -8397,18 +8451,18 @@
       </c>
       <c r="M18" s="26"/>
       <c r="N18" s="26" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>3</v>
@@ -8416,7 +8470,7 @@
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
@@ -8431,7 +8485,7 @@
       </c>
       <c r="M19" s="26"/>
       <c r="N19" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8804,173 +8858,173 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12"/>
       <c r="B6" s="12" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COUNTA('Hazard Analysis'!$A$5:$A$44)</f>
         <v>16</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C7" s="38" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$M$5:$M$44,"Not acceptable*")</f>
         <v>9</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12"/>
       <c r="B8" s="12" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C8" s="36" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$V$5:$V$44,"Acceptable*")</f>
         <v>11</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C9" s="38" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$V$5:$V$44,"Not acceptable*")</f>
         <v>4</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$A$5:$A$44,"&lt;&gt;",'Hazard Analysis'!$P$5:$P$44,"&lt;&gt;",'Hazard Analysis'!$R$5:$R$44,"")</f>
         <v>0</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C11" s="38" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$V$5:$V$44,"*S only*")</f>
         <v>0</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">COUNTIFS('Hazard Analysis'!$A$5:$A$44,"&lt;&gt;",'Hazard Analysis'!$X$5:$X$44,"&lt;&gt;Complete")</f>
         <v>2</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C13" s="38" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$Q$5:$Q$44,3)</f>
         <v>3</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
       <c r="B14" s="12" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">COUNTIF('Hazard Analysis'!$Y$5:$Y$44,"Y*")</f>
         <v>2</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8978,10 +9032,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -8991,10 +9045,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -9004,10 +9058,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -9017,10 +9071,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -9030,10 +9084,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -9043,10 +9097,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -9056,10 +9110,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -9069,10 +9123,10 @@
         <v>8</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -9082,29 +9136,29 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="42" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C29" s="43" t="n">
         <f aca="false">COUNTIF($E$19:$E$27,"Yes")</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="42" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C30" s="44"/>
       <c r="D30" s="44"/>
@@ -9112,7 +9166,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="42" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
@@ -9161,85 +9215,85 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="L5" s="29" t="str">
         <f aca="false">IF($A5="","",IF(AND($A5&lt;&gt;"OVERALL",COUNTIF('Hazard Analysis'!$A$5:$A$44,$A5)=0),"Hazard ID not in Hazard Analysis",IF(AND($A5&lt;&gt;"OVERALL",$C5=""),"No justification that control is impracticable",IF(OR($E5="",$F5="",$G5=""),"Benefit not characterised (magnitude, probability, duration)",IF($H5="","No clinical evidence cited",IF($I5="","State of the art not addressed",IF($J5="","No conclusion",IF($K5="","Not approved","Complete"))))))))</f>
@@ -9248,37 +9302,37 @@
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>549</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>550</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>542</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>543</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>544</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>535</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>536</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>537</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>538</v>
-      </c>
       <c r="H6" s="26" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="L6" s="32" t="str">
         <f aca="false">IF($A6="","",IF(AND($A6&lt;&gt;"OVERALL",COUNTIF('Hazard Analysis'!$A$5:$A$44,$A6)=0),"Hazard ID not in Hazard Analysis",IF(AND($A6&lt;&gt;"OVERALL",$C6=""),"No justification that control is impracticable",IF(OR($E6="",$F6="",$G6=""),"Benefit not characterised (magnitude, probability, duration)",IF($H6="","No clinical evidence cited",IF($I6="","State of the art not addressed",IF($J6="","No conclusion",IF($K6="","Not approved","Complete"))))))))</f>
@@ -9287,37 +9341,37 @@
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B7" s="26" t="s">
+        <v>553</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>542</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>543</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>544</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>555</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>556</v>
+      </c>
+      <c r="J7" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="K7" s="26" t="s">
         <v>548</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>535</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>536</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>537</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>538</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>549</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>550</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>541</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>542</v>
       </c>
       <c r="L7" s="29" t="str">
         <f aca="false">IF($A7="","",IF(AND($A7&lt;&gt;"OVERALL",COUNTIF('Hazard Analysis'!$A$5:$A$44,$A7)=0),"Hazard ID not in Hazard Analysis",IF(AND($A7&lt;&gt;"OVERALL",$C7=""),"No justification that control is impracticable",IF(OR($E7="",$F7="",$G7=""),"Benefit not characterised (magnitude, probability, duration)",IF($H7="","No clinical evidence cited",IF($I7="","State of the art not addressed",IF($J7="","No conclusion",IF($K7="","Not approved","Complete"))))))))</f>
@@ -9326,37 +9380,37 @@
     </row>
     <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="L8" s="32" t="str">
         <f aca="false">IF($A8="","",IF(AND($A8&lt;&gt;"OVERALL",COUNTIF('Hazard Analysis'!$A$5:$A$44,$A8)=0),"Hazard ID not in Hazard Analysis",IF(AND($A8&lt;&gt;"OVERALL",$C8=""),"No justification that control is impracticable",IF(OR($E8="",$F8="",$G8=""),"Benefit not characterised (magnitude, probability, duration)",IF($H8="","No clinical evidence cited",IF($I8="","State of the art not addressed",IF($J8="","No conclusion",IF($K8="","Not approved","Complete"))))))))</f>
@@ -9365,29 +9419,29 @@
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
@@ -9561,115 +9615,115 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B5" s="45" t="n">
         <v>46085</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="M5" s="26" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="N5" s="26" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="O5" s="45" t="n">
         <v>46127</v>
@@ -9686,51 +9740,51 @@
         <v>OK</v>
       </c>
       <c r="S5" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B6" s="45" t="n">
         <v>46161</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>591</v>
+      </c>
+      <c r="E6" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>585</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>578</v>
-      </c>
       <c r="F6" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J6" s="26" t="s">
+        <v>592</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>586</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>580</v>
-      </c>
       <c r="M6" s="26" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="O6" s="45" t="n">
         <v>46204</v>
@@ -9747,51 +9801,51 @@
         <v>OK</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B7" s="45" t="n">
         <v>46211</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="M7" s="26" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="N7" s="26" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="O7" s="45" t="n">
         <v>46326</v>
@@ -9806,51 +9860,51 @@
         <v>OK</v>
       </c>
       <c r="S7" s="26" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B8" s="45" t="n">
         <v>46259</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="O8" s="45" t="n">
         <v>46295</v>
@@ -9867,47 +9921,47 @@
         <v>OK</v>
       </c>
       <c r="S8" s="26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B9" s="45" t="n">
         <v>46267</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
       <c r="M9" s="26" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="N9" s="26" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="O9" s="45" t="n">
         <v>46305</v>
@@ -9922,7 +9976,7 @@
         <v>Risk file rows not updated</v>
       </c>
       <c r="S9" s="26" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10647,38 +10701,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10686,10 +10740,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -10702,10 +10756,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -10718,10 +10772,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -10734,10 +10788,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -10750,10 +10804,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -10766,10 +10820,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -10782,10 +10836,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -10798,10 +10852,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -10814,10 +10868,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -10830,10 +10884,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -10846,10 +10900,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -10862,10 +10916,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -10878,10 +10932,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -10894,10 +10948,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -10910,10 +10964,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -10926,10 +10980,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -10942,10 +10996,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -10958,10 +11012,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -10974,10 +11028,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -10990,10 +11044,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -11006,10 +11060,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -11022,10 +11076,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -11038,10 +11092,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -11054,10 +11108,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -11070,10 +11124,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -11086,10 +11140,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -11102,10 +11156,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -11118,10 +11172,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -11134,10 +11188,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
@@ -11150,10 +11204,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -11163,7 +11217,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="42" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D36" s="50" t="str">
         <f aca="false">IF(COUNTA($G$5:$G$34)=0,"Not started",COUNTIF($G$5:$G$34,"Yes") &amp; " of " &amp; (COUNTA($G$5:$G$34)-COUNTIF($G$5:$G$34,"N/A")) &amp; " applicable records present")</f>
